--- a/excel_templates/通知表.xlsx
+++ b/excel_templates/通知表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1148,15 +1148,1527 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-02-11 15:14:03</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>e6e73373-3cec-4333-bca6-2edf258bf04e</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>您借用的设备「手机-001」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>手机-001</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>PHO001</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40:00</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>664331dd-5c65-45a8-b55b-fb4c450f9cdb</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>您借用的设备「LE- 
+XFZN01-2」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>LE- 
+XFZN01-2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40:16</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4907d31b-adc4-45fc-b178-e9a27bb00420</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>您借用的设备「仪表-004」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>qwqe4</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40:17</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>18fde116-4b52-4479-949c-9b88f33d33b4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>您借用的设备「仪表-005」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>仪表-005</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>qwqe5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40:19</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>051d9458-13d7-4169-b195-42b5c1b89994</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>您借用的设备「手机-001」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>手机-001</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PHO001</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40:20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>f2fb23ed-7809-4245-8ba9-5d6040fe03d5</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>45211578-f369-4bc7-9a03-996621c08b86</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>summer</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>您借用的设备「手机-002」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>手机-002</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>PHO002</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-02-11 15:14:03</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40:21</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3a053c8e-e185-44f3-8088-226904116fd5</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>您借用的设备「手机-LOST-001」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40:23</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>092f5445-70c5-4f78-aa3b-428493ea742f</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>您借用的设备「联想平板-邵阳K12（HA27VAW9）」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>联想平板-邵阳K12（HA27VAW9）</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>TEG-243</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40:25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dc2d3fec-bdc2-4589-88e5-ca2ef32a1371</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>您借用的设备「机械臂（大象机器人）」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>机械臂（大象机器人）</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>TEG-238</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40:26</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>a5b50f29-57b7-4dab-9914-03deee3ccb03</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>您借用的设备「iPhone 14 Pro」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>iPhone 14 Pro</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>TEG-199</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40:28</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>7ce41a13-e6a4-45fe-84dc-cea598e50b63</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>您借用的设备「联通测试卡：18696137226」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>联通测试卡：18696137226</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ybb01</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40:29</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>d0607546-fe0b-4187-91ce-a2ed33ee6104</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>您借用的设备「测试卡17320507707」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>测试卡17320507707</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ybb02</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:40:31</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3c3358a3-750c-4e18-afa0-993871ab51f5</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>您借用的设备「LE- 
+XFZN01-2」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>LE- 
+XFZN01-2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42:44</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>9624b199-07c7-4f07-b8a5-05412790f516</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>您借用的设备「仪表-004」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>qwqe4</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42:46</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>05ce1303-5b1a-4ca7-9e75-2a3ef1a54cfb</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>您借用的设备「仪表-005」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>仪表-005</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>qwqe5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42:47</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>8cee9d20-309d-4969-874d-a6ddfb83a759</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>您借用的设备「手机-001」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>手机-001</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>PHO001</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42:48</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>a961b4b4-7352-4eb1-ac19-d193c2593cce</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>45211578-f369-4bc7-9a03-996621c08b86</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>summer</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>您借用的设备「手机-002」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>手机-002</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>PHO002</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42:49</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>86c5739a-3249-4832-b5ec-847349b62da3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>您借用的设备「手机-LOST-001」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42:51</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1564ba59-7bce-4c55-a480-9478c25db6e5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>您借用的设备「联想平板-邵阳K12（HA27VAW9）」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>联想平板-邵阳K12（HA27VAW9）</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>TEG-243</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42:52</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>e16f14d6-63c6-4b16-b85e-d7d15d9daef1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>您借用的设备「机械臂（大象机器人）」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>机械臂（大象机器人）</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>TEG-238</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42:53</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>32c89b69-5b16-489f-add3-003b987c8844</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>您借用的设备「iPhone 14 Pro」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>iPhone 14 Pro</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>TEG-199</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42:54</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ea280b87-22ea-462b-8db7-815ef8a31141</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>您借用的设备「联通测试卡：18696137226」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>联通测试卡：18696137226</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ybb01</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42:56</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>a868fcb9-fce0-4d91-a4e4-d442d90792bb</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>您借用的设备「测试卡17320507707」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>测试卡17320507707</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ybb02</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:42:57</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cfb57627-d4dd-4869-abf5-ea034b042d96</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>设备强制归还通知</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>操作员 admin 已将您借用的设备「手机-001」强制归还。</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>手机-001</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>PHO001</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:12:02</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1fbd3ac0-161d-4b40-a888-14f586596e04</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>设备强制归还通知</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>操作员 admin 已将您借用的设备「手机-LOST-001」强制归还。</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:13:05</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>c7fb7ae7-3f37-402b-bf05-9dbedb8df019</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>您借用的设备「联想平板-邵阳K12（HA27VAW9）」已逾期，请及时归还。如有问题请联系管理员 admin。</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>联想平板-邵阳K12（HA27VAW9）</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>TEG-243</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:15:59</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4001a0b3-4ebd-4800-8453-771be4445b3d</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>您借用的设备「联想平板-邵阳K12（HA27VAW9）」已逾期，请及时归还。</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>联想平板-邵阳K12（HA27VAW9）</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>TEG-243</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:17:52</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>9185ec3e-82e9-44bc-8d26-427bd32ca5a8</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>设备逾期归还提醒</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>您借用的设备「联想平板-邵阳K12（HA27VAW9）」已逾期，请及时归还。如有问题请联系管理员。</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>联想平板-邵阳K12（HA27VAW9）</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>TEG-243</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:18:35</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>869b2e23-7eac-427d-a4fd-ff741f2bd30f</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>设备强制归还通知</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>操作员 admin 已将您借用的设备「仪表-005」强制归还。</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>仪表-005</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>qwqe5</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-02-24 13:48:29</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>warning</t>
         </is>

--- a/excel_templates/通知表.xlsx
+++ b/excel_templates/通知表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2674,6 +2674,528 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>6f93e95e-fd5e-411f-a4b0-2609419d4766</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>设备强制归还通知</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>操作员 lan 已将您借用的设备「LE- 
+XFZN01-2」强制归还。</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>LE- 
+XFZN01-2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>20a7b8fd-d41d-4a97-9617-93c7dbbdcc04</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:23:36</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>761821d1-4163-4c53-9484-b4dc5531ddce</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>设备转借通知</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>您借用的设备「仪表-004」已被 test 转借给 lan。</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>qwqe4</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:30:09</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cde1ff05-fe46-479a-849b-d4a55ad3bfe5</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>设备转借通知</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>操作员 test 已将设备「仪表-004」转借给您。</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>qwqe4</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:30:10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ac40e432-bd65-470f-bc4b-083ab851a4fb</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>设备转借通知</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>操作员 lan 已将设备「仪表-004」转借给您。</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>qwqe4</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:16:03</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>8b525b68-f1be-4e26-9cf7-afd9e107b480</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>设备归还通知</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>您保管的设备「手机-LOST-001」已被 test 归还。</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:16:55</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>66a8e23f-1075-4cbc-aacf-12395bb6e67e</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>设备归还通知</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>您保管的设备「手机-LOST-001」已被 test 归还。</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:16:56</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ffbb2671-7e7f-4241-9a61-4434366f078b</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>设备保管人变更通知</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>设备「手机-LOST-001」的保管人已从 lan 转让给您。</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:20:34</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>b1c78e21-3752-46d8-8c3e-999e82bdb4b1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>设备被转借通知</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>您借用的设备「仪表-004」已被 test 转借走。</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>仪表-004</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>qwqe4</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:27:13</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ccc1d3ba-2249-4302-b638-eb1ec64031a5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>设备被借用通知</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>您保管的设备「手机-LOST-001」已被 lan 借用。</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:37:20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>info</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>872beb37-0584-46c7-a8c8-b9d69c377d76</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>设备强制归还通知</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>操作员 保管人 test 已将您借用的设备「手机-LOST-001」强制归还。</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>手机-LOST-001</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>cea5f628-8066-466c-8c8b-dc0d66e106f0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:38:04</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
